--- a/public/templates/qitaat-provider-branches-template.xlsx
+++ b/public/templates/qitaat-provider-branches-template.xlsx
@@ -1,56 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="README" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000E9E6F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E7EB"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -65,14 +71,86 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -151,7 +229,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -186,7 +263,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -221,16 +297,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -352,277 +432,260 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" customWidth="1"/>
-    <col min="14" max="14" width="24.83203125" customWidth="1"/>
-    <col min="15" max="15" width="14.83203125" customWidth="1"/>
-    <col min="16" max="16" width="14.83203125" customWidth="1"/>
-    <col min="17" max="17" width="14.83203125" customWidth="1"/>
-    <col min="18" max="18" width="14.83203125" customWidth="1"/>
-    <col min="19" max="19" width="14.83203125" customWidth="1"/>
-    <col min="20" max="20" width="14.83203125" customWidth="1"/>
-    <col min="21" max="21" width="16.83203125" customWidth="1"/>
-    <col min="22" max="22" width="14.83203125" customWidth="1"/>
-    <col min="23" max="23" width="16.83203125" customWidth="1"/>
-    <col min="24" max="24" width="23.83203125" customWidth="1"/>
-    <col min="25" max="25" width="14.83203125" customWidth="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>provider_cr_number</v>
-      </c>
-      <c r="B1" t="str">
-        <v>provider_legal_name_ar</v>
-      </c>
-      <c r="C1" t="str">
-        <v>branch_name_ar</v>
-      </c>
-      <c r="D1" t="str">
-        <v>branch_name_en</v>
-      </c>
-      <c r="E1" t="str">
-        <v>branch_type</v>
-      </c>
-      <c r="F1" t="str">
-        <v>is_main</v>
-      </c>
-      <c r="G1" t="str">
-        <v>is_active</v>
-      </c>
-      <c r="H1" t="str">
-        <v>country</v>
-      </c>
-      <c r="I1" t="str">
-        <v>region</v>
-      </c>
-      <c r="J1" t="str">
-        <v>city</v>
-      </c>
-      <c r="K1" t="str">
-        <v>district</v>
-      </c>
-      <c r="L1" t="str">
-        <v>street_name</v>
-      </c>
-      <c r="M1" t="str">
-        <v>building_number</v>
-      </c>
-      <c r="N1" t="str">
-        <v>short_national_address</v>
-      </c>
-      <c r="O1" t="str">
-        <v>full_address</v>
-      </c>
-      <c r="P1" t="str">
-        <v>postal_code</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>latitude</v>
-      </c>
-      <c r="R1" t="str">
-        <v>longitude</v>
-      </c>
-      <c r="S1" t="str">
-        <v>phone</v>
-      </c>
-      <c r="T1" t="str">
-        <v>mobile</v>
-      </c>
-      <c r="U1" t="str">
-        <v>unified_number</v>
-      </c>
-      <c r="V1" t="str">
-        <v>email</v>
-      </c>
-      <c r="W1" t="str">
-        <v>contact_person</v>
-      </c>
-      <c r="X1" t="str">
-        <v>working_hours_summary</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1010XXXXXX</v>
-      </c>
-      <c r="B2" t="str">
-        <v>مؤسسة المثال للألمنيوم</v>
-      </c>
-      <c r="C2" t="str">
-        <v>الفرع الرئيسي - جدة</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Main Branch - Jeddah</v>
-      </c>
-      <c r="E2" t="str">
-        <v>main</v>
-      </c>
-      <c r="F2" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="G2" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="H2" t="str">
-        <v>SA</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Makkah</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Jeddah</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Al Salamah</v>
-      </c>
-      <c r="L2" t="str">
-        <v>King Abdulaziz Rd</v>
-      </c>
-      <c r="M2" t="str">
-        <v>1234</v>
-      </c>
-      <c r="N2" t="str">
-        <v>JEXX1234</v>
-      </c>
-      <c r="O2" t="str">
-        <v>King Abdulaziz Rd, Jeddah</v>
-      </c>
-      <c r="P2" t="str">
-        <v>23525</v>
-      </c>
-      <c r="Q2">
-        <v>21.5433</v>
-      </c>
-      <c r="R2">
-        <v>39.1728</v>
-      </c>
-      <c r="S2" t="str">
-        <v>+96612XXXXXXX</v>
-      </c>
-      <c r="T2" t="str">
-        <v>+9665XXXXXXXX</v>
-      </c>
-      <c r="U2" t="str">
-        <v>7000XXXXXX</v>
-      </c>
-      <c r="V2" t="str">
-        <v>jeddah@example.sa</v>
-      </c>
-      <c r="W2" t="str">
-        <v>Ahmed Ali</v>
-      </c>
-      <c r="X2" t="str">
-        <v>Sun-Thu 08:00-17:00</v>
-      </c>
-      <c r="Y2" t="str">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name_ar</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unified_number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>commercial_registration</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>branch_name_ar</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>branch_name_en</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>national_short_address</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>street_address</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>google_maps_url</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>branch_phone</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>branch_email</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>is_primary_branch</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>working_hours</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>branch_notes</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="90.83203125" customWidth="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Qitaat Provider Intake Template</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>DO NOT remove or rename the header row.</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Qitaat — Provider branches template</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>One row per record. Do not include real PII in shared copies.</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Field / Topic</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Encoding: UTF-8. Phones: E.164 (+9665XXXXXXXX). Booleans: TRUE/FALSE.</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Encoding</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Coordinates: decimal degrees (lat, lng).</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Link key</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Use commercial_registration OR unified_number to match provider</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>is_primary_branch</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TRUE / FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>working_hours</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Free text summary (e.g., Sun-Thu 08:00-17:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Coordinates</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Decimal degrees</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>national_short_address</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Short National Address code</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>No row is auto-imported. Branches are created manually after provider conversion.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A5"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>